--- a/data/trans_dic/P39A1_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P39A1_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar, mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar, mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 90,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>75,63; 85,08</t>
+          <t>75,25; 85,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,64; 87,56</t>
+          <t>80,57; 87,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79,45; 85,33</t>
+          <t>79,34; 85,39</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>67,79; 77,58</t>
+          <t>67,73; 77,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,12; 70,0</t>
+          <t>62,65; 70,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66,48; 72,96</t>
+          <t>66,13; 72,46</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51,18; 62,83</t>
+          <t>51,76; 62,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42,82; 52,83</t>
+          <t>43,72; 53,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48,78; 56,66</t>
+          <t>48,24; 56,11</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>91,11; 96,86</t>
+          <t>91,31; 96,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,34; 92,78</t>
+          <t>40,97; 93,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54,87; 94,0</t>
+          <t>56,33; 93,92</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,63; 37,6</t>
+          <t>25,79; 38,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,75; 24,58</t>
+          <t>16,61; 24,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,67; 28,88</t>
+          <t>21,69; 28,75</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>72,67; 82,59</t>
+          <t>72,93; 82,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>74,47; 83,29</t>
+          <t>74,48; 83,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75,46; 81,95</t>
+          <t>75,2; 82,06</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,96; 51,03</t>
+          <t>40,95; 51,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>44,66; 81,11</t>
+          <t>44,77; 80,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44,91; 72,7</t>
+          <t>45,05; 72,75</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>91,99; 97,82</t>
+          <t>92,03; 97,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>88,69; 93,86</t>
+          <t>88,87; 93,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>91,84; 96,5</t>
+          <t>91,63; 96,21</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>70,24; 80,19</t>
+          <t>70,44; 79,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>65,0; 74,24</t>
+          <t>64,76; 74,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>68,27; 74,97</t>
+          <t>68,32; 75,12</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar, mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar, mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 90,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>234025; 263254</t>
+          <t>232847; 264972</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>228770; 248394</t>
+          <t>228564; 247750</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>471249; 506098</t>
+          <t>470570; 506456</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>343672; 393331</t>
+          <t>343382; 394696</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>299334; 337321</t>
+          <t>301899; 337712</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>657385; 721492</t>
+          <t>653928; 716481</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>138394; 169907</t>
+          <t>139969; 170338</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>125011; 154256</t>
+          <t>127657; 156056</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>274335; 318658</t>
+          <t>271322; 315569</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>221827; 235816</t>
+          <t>222319; 236109</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>153674; 336755</t>
+          <t>148697; 337709</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>332725; 570024</t>
+          <t>341627; 569569</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>45275; 66417</t>
+          <t>45560; 67351</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34507; 50653</t>
+          <t>34220; 50241</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>82947; 110522</t>
+          <t>83023; 110035</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>176057; 200094</t>
+          <t>176689; 200708</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>162143; 181347</t>
+          <t>162168; 181778</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>347089; 376943</t>
+          <t>345915; 377461</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>237327; 295716</t>
+          <t>237291; 297731</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>353278; 641580</t>
+          <t>354161; 634568</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>615513; 996316</t>
+          <t>617466; 997018</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>798225; 848851</t>
+          <t>798591; 848847</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>591957; 626452</t>
+          <t>593164; 625821</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1409967; 1481408</t>
+          <t>1406706; 1477087</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2245141; 2563337</t>
+          <t>2251465; 2526047</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2146870; 2451928</t>
+          <t>2138889; 2451416</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4437255; 4872637</t>
+          <t>4440457; 4882168</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A1_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P39A1_2023-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,69%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>75,25; 85,63</t>
+          <t>75,85; 84,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,57; 87,33</t>
+          <t>81,59; 88,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79,34; 85,39</t>
+          <t>79,9; 85,15</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,49%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>67,73; 77,85</t>
+          <t>67,25; 76,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,65; 70,08</t>
+          <t>62,85; 70,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66,13; 72,46</t>
+          <t>66,23; 72,27</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>51,98%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51,76; 62,99</t>
+          <t>50,83; 62,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43,72; 53,45</t>
+          <t>43,07; 52,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48,24; 56,11</t>
+          <t>47,97; 55,66</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>91,31; 96,98</t>
+          <t>88,55; 96,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,97; 93,04</t>
+          <t>89,03; 94,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,33; 93,92</t>
+          <t>90,27; 94,79</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,79; 38,13</t>
+          <t>27,58; 39,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,61; 24,38</t>
+          <t>17,48; 25,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,69; 28,75</t>
+          <t>23,52; 30,3</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,2%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>72,93; 82,85</t>
+          <t>73,04; 82,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>74,48; 83,49</t>
+          <t>73,34; 82,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75,2; 82,06</t>
+          <t>74,53; 81,35</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>45,45%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,95; 51,38</t>
+          <t>42,24; 51,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>44,77; 80,22</t>
+          <t>41,0; 48,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45,05; 72,75</t>
+          <t>42,33; 48,3</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>92,59%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>92,03; 97,82</t>
+          <t>90,55; 94,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>88,87; 93,77</t>
+          <t>89,95; 93,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>91,63; 96,21</t>
+          <t>91,02; 93,86</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>69,47%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>70,44; 79,03</t>
+          <t>69,08; 72,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>64,76; 74,22</t>
+          <t>66,72; 69,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>68,32; 75,12</t>
+          <t>68,31; 70,5</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>250608</t>
+          <t>255152</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>239463</t>
+          <t>264701</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>490072</t>
+          <t>519853</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>232847; 264972</t>
+          <t>240430; 267707</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>228564; 247750</t>
+          <t>254287; 274322</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>470570; 506456</t>
+          <t>502315; 535300</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>369366</t>
+          <t>373912</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>318928</t>
+          <t>341419</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>688294</t>
+          <t>715331</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>343382; 394696</t>
+          <t>348236; 396559</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>301899; 337712</t>
+          <t>321466; 360079</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>653928; 716481</t>
+          <t>681790; 743953</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>155178</t>
+          <t>152674</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>140752</t>
+          <t>141385</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>295930</t>
+          <t>294059</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>139969; 170338</t>
+          <t>136617; 167980</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>127657; 156056</t>
+          <t>127899; 156513</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>271322; 315569</t>
+          <t>271358; 314899</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>230059</t>
+          <t>261717</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>270332</t>
+          <t>301977</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>500390</t>
+          <t>563695</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>222319; 236109</t>
+          <t>247884; 269160</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>148697; 337709</t>
+          <t>291785; 310797</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>341627; 569569</t>
+          <t>548545; 576056</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>55459</t>
+          <t>66695</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>41447</t>
+          <t>47541</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96907</t>
+          <t>114236</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>45560; 67351</t>
+          <t>56062; 79464</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34220; 50241</t>
+          <t>39256; 57942</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>83023; 110035</t>
+          <t>100616; 129638</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>189793</t>
+          <t>185954</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>172449</t>
+          <t>174920</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>362242</t>
+          <t>360874</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>176689; 200708</t>
+          <t>173929; 196957</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>162168; 181778</t>
+          <t>163805; 183996</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>345915; 377461</t>
+          <t>343957; 375405</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>266921</t>
+          <t>308155</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>473254</t>
+          <t>311261</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>740175</t>
+          <t>619416</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>237291; 297731</t>
+          <t>280586; 341720</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>354161; 634568</t>
+          <t>286506; 336615</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>617466; 997018</t>
+          <t>576994; 658263</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>823611</t>
+          <t>670041</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>614532</t>
+          <t>709472</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1438143</t>
+          <t>1379512</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>798591; 848847</t>
+          <t>652616; 683464</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>593164; 625821</t>
+          <t>691980; 722324</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1406706; 1477087</t>
+          <t>1356216; 1398568</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2340996</t>
+          <t>2274301</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2271157</t>
+          <t>2292676</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4612153</t>
+          <t>4566977</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2251465; 2526047</t>
+          <t>2217596; 2329826</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2138889; 2451416</t>
+          <t>2244329; 2337865</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4440457; 4882168</t>
+          <t>4490424; 4634367</t>
         </is>
       </c>
     </row>
